--- a/data/trans_camb/P2A_lim_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,97</t>
+          <t>-0,9; 5,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,73</t>
+          <t>-2,68; 2,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 10,28</t>
+          <t>2,97; 10,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 7,65</t>
+          <t>-1,26; 7,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 3,83</t>
+          <t>-3,49; 3,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,19; 7,21</t>
+          <t>0,2; 7,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,41</t>
+          <t>-0,17; 5,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,5</t>
+          <t>-2,23; 2,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,07</t>
+          <t>3,21; 8,18</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 188,42</t>
+          <t>-21,23; 172,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-48,47; 96,69</t>
+          <t>-47,46; 88,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55,45; 323,33</t>
+          <t>42,9; 318,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 215,39</t>
+          <t>-19,96; 202,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,33; 114,16</t>
+          <t>-48,99; 99,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 212,66</t>
+          <t>1,44; 223,92</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 140,7</t>
+          <t>-5,4; 140,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,61; 65,65</t>
+          <t>-37,22; 69,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>43,04; 212,66</t>
+          <t>50,35; 209,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,1</t>
+          <t>-2,08; 5,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 3,21</t>
+          <t>-3,55; 3,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,48; 7,8</t>
+          <t>0,05; 7,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 5,5</t>
+          <t>-2,15; 5,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,13</t>
+          <t>-4,08; 2,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 7,05</t>
+          <t>-0,15; 6,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,11</t>
+          <t>-1,0; 4,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,21</t>
+          <t>-2,57; 2,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,19</t>
+          <t>1,31; 6,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 135,57</t>
+          <t>-31,56; 144,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 85,07</t>
+          <t>-46,66; 94,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 221,69</t>
+          <t>-0,63; 207,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-29,45; 132,0</t>
+          <t>-26,48; 144,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,63; 74,43</t>
+          <t>-54,72; 81,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 175,06</t>
+          <t>-4,73; 178,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,0; 86,34</t>
+          <t>-14,98; 94,64</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,26; 50,97</t>
+          <t>-37,71; 48,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 147,19</t>
+          <t>13,53; 142,03</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 9,16</t>
+          <t>2,01; 9,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 4,29</t>
+          <t>-2,0; 4,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 10,87</t>
+          <t>-4,19; 11,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 5,37</t>
+          <t>-6,0; 5,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 4,42</t>
+          <t>-8,51; 4,86</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 11,22</t>
+          <t>-2,59; 11,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 6,95</t>
+          <t>1,03; 6,97</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 3,29</t>
+          <t>-2,45; 3,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 9,4</t>
+          <t>-3,16; 9,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,19; 185,88</t>
+          <t>25,61; 177,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-23,51; 85,25</t>
+          <t>-25,77; 93,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,07; 175,33</t>
+          <t>-53,26; 197,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 86,54</t>
+          <t>-44,54; 83,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-66,18; 64,12</t>
+          <t>-64,81; 75,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,7; 163,31</t>
+          <t>-20,62; 161,68</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,12; 116,94</t>
+          <t>8,54; 111,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,36; 57,82</t>
+          <t>-28,56; 55,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 141,13</t>
+          <t>-31,98; 135,68</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,48</t>
+          <t>0,58; 5,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,46</t>
+          <t>-2,87; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,89; 9,17</t>
+          <t>3,98; 9,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,82</t>
+          <t>1,72; 7,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 3,89</t>
+          <t>-2,18; 3,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 57,46</t>
+          <t>2,66; 55,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,65</t>
+          <t>1,98; 5,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,71</t>
+          <t>-1,91; 1,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 35,87</t>
+          <t>4,76; 44,4</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,02; 78,74</t>
+          <t>5,9; 81,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,39; 20,91</t>
+          <t>-31,48; 23,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41,9; 127,18</t>
+          <t>43,31; 135,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,57; 119,87</t>
+          <t>15,72; 118,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 60,22</t>
+          <t>-22,14; 57,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,94; 927,05</t>
+          <t>29,96; 806,18</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,77; 78,01</t>
+          <t>21,99; 82,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-18,55; 23,69</t>
+          <t>-20,87; 23,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>57,55; 500,14</t>
+          <t>57,96; 611,64</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,43</t>
+          <t>-3,62; 4,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 4,34</t>
+          <t>-3,63; 4,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,54; 17,33</t>
+          <t>7,69; 17,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,22; 9,29</t>
+          <t>1,79; 8,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 6,35</t>
+          <t>-0,88; 6,1</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,66; 10,57</t>
+          <t>2,0; 10,72</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,07</t>
+          <t>1,01; 6,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,19</t>
+          <t>-0,96; 4,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,04</t>
+          <t>5,85; 12,11</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-33,02; 70,59</t>
+          <t>-32,79; 80,48</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 75,24</t>
+          <t>-32,73; 64,93</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65,74; 287,33</t>
+          <t>69,0; 288,05</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18,36; 135,71</t>
+          <t>16,5; 130,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-8,08; 96,75</t>
+          <t>-9,66; 90,92</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,29; 149,83</t>
+          <t>23,06; 152,68</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,19; 82,87</t>
+          <t>9,5; 90,31</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 59,06</t>
+          <t>-9,73; 57,98</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>55,33; 169,87</t>
+          <t>61,09; 169,84</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 8,56</t>
+          <t>-0,7; 8,31</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 5,98</t>
+          <t>-2,06; 6,11</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 6,56</t>
+          <t>-3,2; 6,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 4,78</t>
+          <t>-0,3; 4,85</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 2,97</t>
+          <t>-1,94; 2,88</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,26; 12,67</t>
+          <t>7,1; 12,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,71</t>
+          <t>0,32; 4,76</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,81</t>
+          <t>-1,49; 2,79</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,26</t>
+          <t>4,96; 9,94</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-14,74; 267,06</t>
+          <t>-15,98; 293,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 189,76</t>
+          <t>-35,38; 223,44</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,37; 190,32</t>
+          <t>-52,78; 199,88</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 61,91</t>
+          <t>-3,22; 64,6</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 37,6</t>
+          <t>-20,01; 35,65</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>70,84; 162,0</t>
+          <t>70,0; 162,59</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4,71; 64,81</t>
+          <t>2,93; 65,55</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 39,78</t>
+          <t>-16,41; 39,82</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>57,22; 144,27</t>
+          <t>53,36; 136,17</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,2</t>
+          <t>1,47; 4,28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 1,67</t>
+          <t>-0,95; 1,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,93</t>
+          <t>3,05; 7,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,88</t>
+          <t>1,88; 4,91</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,9</t>
+          <t>-0,71; 1,96</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,28; 26,45</t>
+          <t>5,38; 25,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,12; 4,08</t>
+          <t>2,17; 4,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,44</t>
+          <t>-0,41; 1,48</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,43; 16,29</t>
+          <t>5,51; 16,8</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>20,24; 70,18</t>
+          <t>20,07; 70,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 27,35</t>
+          <t>-12,96; 29,31</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>48,56; 130,02</t>
+          <t>48,28; 126,42</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,52; 67,56</t>
+          <t>21,12; 65,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 26,14</t>
+          <t>-8,12; 25,85</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>63,66; 338,57</t>
+          <t>64,47; 315,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,58; 60,09</t>
+          <t>27,18; 59,75</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 20,14</t>
+          <t>-4,99; 21,62</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>72,23; 221,05</t>
+          <t>72,96; 246,68</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>6,61</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,67</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5,56</t>
+          <t>5,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 5,72</t>
+          <t>-1,13; 5,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,76</t>
+          <t>-2,68; 2,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 10,19</t>
+          <t>3,6; 10,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 7,69</t>
+          <t>-1,03; 7,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 3,55</t>
+          <t>-3,46; 4,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 7,71</t>
+          <t>-0,15; 6,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 5,52</t>
+          <t>-0,05; 5,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 2,41</t>
+          <t>-2,07; 2,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,18</t>
+          <t>2,86; 7,8</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>154,27%</t>
+          <t>147,34%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115,16%</t>
+          <t>109,61%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 172,08</t>
+          <t>-20,85; 187,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-47,46; 88,03</t>
+          <t>-48,14; 98,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,9; 318,81</t>
+          <t>52,34; 308,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 202,36</t>
+          <t>-19,48; 207,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-48,99; 99,25</t>
+          <t>-48,65; 110,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 223,92</t>
+          <t>-3,25; 185,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 140,49</t>
+          <t>-3,35; 135,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 69,47</t>
+          <t>-35,25; 63,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50,35; 209,48</t>
+          <t>40,31; 208,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,96</t>
+          <t>3,82</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,52</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>3,64</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 5,13</t>
+          <t>-2,01; 5,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,4</t>
+          <t>-3,3; 3,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,62</t>
+          <t>0,25; 7,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 5,53</t>
+          <t>-2,0; 5,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 2,92</t>
+          <t>-3,9; 3,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 6,72</t>
+          <t>0,27; 7,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,09</t>
+          <t>-0,93; 4,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,13</t>
+          <t>-2,7; 2,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,21</t>
+          <t>1,2; 6,19</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 144,88</t>
+          <t>-30,36; 130,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-46,66; 94,07</t>
+          <t>-46,08; 87,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 207,6</t>
+          <t>2,17; 195,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-26,48; 144,92</t>
+          <t>-29,74; 142,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,72; 81,06</t>
+          <t>-52,84; 82,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 178,57</t>
+          <t>0,02; 194,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 94,64</t>
+          <t>-15,46; 98,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 48,38</t>
+          <t>-39,1; 47,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,53; 142,03</t>
+          <t>15,81; 139,59</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>8,82</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,46</t>
+          <t>4,42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,8</t>
+          <t>7,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,14</t>
+          <t>2,03; 8,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 4,45</t>
+          <t>-1,8; 4,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 11,44</t>
+          <t>5,08; 12,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 5,6</t>
+          <t>-5,97; 5,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 4,86</t>
+          <t>-7,88; 4,5</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 11,0</t>
+          <t>-1,48; 11,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,97</t>
+          <t>1,0; 6,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,36</t>
+          <t>-2,51; 3,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 9,26</t>
+          <t>4,27; 11,15</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>136,92%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>106,36%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25,61; 177,14</t>
+          <t>25,99; 178,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,77; 93,14</t>
+          <t>-23,52; 91,32</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-53,26; 197,4</t>
+          <t>59,51; 246,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 83,53</t>
+          <t>-46,0; 101,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-64,81; 75,55</t>
+          <t>-61,23; 84,33</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,62; 161,68</t>
+          <t>-13,22; 169,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,54; 111,93</t>
+          <t>8,95; 116,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 55,99</t>
+          <t>-28,65; 58,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,98; 135,68</t>
+          <t>44,92; 184,98</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>6,77</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,14</t>
+          <t>3,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>5,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,66</t>
+          <t>0,67; 5,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 1,55</t>
+          <t>-2,65; 1,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,61</t>
+          <t>4,1; 9,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,96</t>
+          <t>1,58; 8,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 3,74</t>
+          <t>-2,08; 3,62</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 55,35</t>
+          <t>0,67; 6,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,84</t>
+          <t>1,8; 5,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,71</t>
+          <t>-1,72; 2,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4,76; 44,4</t>
+          <t>3,62; 7,3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>273,77%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>176,94%</t>
+          <t>67,88%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,9; 81,01</t>
+          <t>7,23; 81,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,48; 23,4</t>
+          <t>-29,88; 26,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43,31; 135,14</t>
+          <t>45,4; 141,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,72; 118,85</t>
+          <t>16,47; 126,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,14; 57,69</t>
+          <t>-22,31; 55,56</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,96; 806,18</t>
+          <t>6,0; 95,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,99; 82,9</t>
+          <t>19,97; 82,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 23,44</t>
+          <t>-19,26; 28,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>57,96; 611,64</t>
+          <t>40,21; 103,76</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12,2</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,18</t>
+          <t>9,5</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>8,99</t>
+          <t>9,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,3</t>
+          <t>-3,74; 4,16</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,07</t>
+          <t>-3,34; 4,31</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,69; 17,33</t>
+          <t>5,01; 13,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 8,88</t>
+          <t>1,74; 8,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 6,1</t>
+          <t>-0,76; 5,56</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 10,72</t>
+          <t>6,06; 12,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,35</t>
+          <t>0,65; 6,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 4,19</t>
+          <t>-1,18; 4,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,85; 12,11</t>
+          <t>7,07; 12,02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148,34%</t>
+          <t>118,01%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>111,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>106,81%</t>
+          <t>113,8%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-32,79; 80,48</t>
+          <t>-36,25; 67,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 64,93</t>
+          <t>-32,03; 75,91</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>69,0; 288,05</t>
+          <t>43,79; 229,71</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16,5; 130,01</t>
+          <t>15,05; 123,59</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 90,92</t>
+          <t>-7,15; 79,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,06; 152,68</t>
+          <t>56,72; 181,17</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,5; 90,31</t>
+          <t>5,19; 84,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,73; 57,98</t>
+          <t>-11,44; 61,79</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>61,09; 169,84</t>
+          <t>69,21; 170,85</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,82</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,56</t>
+          <t>8,07</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 8,31</t>
+          <t>-0,84; 8,11</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 6,11</t>
+          <t>-2,1; 5,78</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 6,17</t>
+          <t>-1,55; 8,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,85</t>
+          <t>0,08; 5,01</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,88</t>
+          <t>-1,87; 2,82</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,1; 12,66</t>
+          <t>6,71; 12,61</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,76</t>
+          <t>0,38; 4,85</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,79</t>
+          <t>-1,46; 2,91</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,96; 9,94</t>
+          <t>5,59; 10,75</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>55,37%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>110,56%</t>
+          <t>109,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>99,88%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 293,4</t>
+          <t>-16,57; 257,77</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-35,38; 223,44</t>
+          <t>-29,7; 213,61</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-52,78; 199,88</t>
+          <t>-30,21; 265,24</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 64,6</t>
+          <t>-1,04; 62,84</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-20,01; 35,65</t>
+          <t>-19,12; 36,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>70,0; 162,59</t>
+          <t>65,03; 161,72</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2,93; 65,55</t>
+          <t>3,63; 67,76</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-16,41; 39,82</t>
+          <t>-16,62; 40,55</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>53,36; 136,17</t>
+          <t>61,52; 149,89</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6,1</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,72</t>
+          <t>6,22</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,49</t>
+          <t>6,52</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,28</t>
+          <t>1,3; 4,23</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,68</t>
+          <t>-0,82; 1,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,82</t>
+          <t>5,22; 8,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,91</t>
+          <t>1,92; 4,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,96</t>
+          <t>-0,74; 2,09</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>5,38; 25,65</t>
+          <t>4,89; 7,58</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,17</t>
+          <t>2,08; 4,26</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,48</t>
+          <t>-0,49; 1,46</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5,51; 16,8</t>
+          <t>5,54; 7,48</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>102,14%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>133,24%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>115,14%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>20,07; 70,87</t>
+          <t>18,41; 70,67</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 29,31</t>
+          <t>-11,55; 26,98</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>48,28; 126,42</t>
+          <t>72,64; 136,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>21,12; 65,93</t>
+          <t>21,78; 65,38</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 25,85</t>
+          <t>-8,76; 28,1</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>64,47; 315,33</t>
+          <t>55,19; 105,3</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>27,18; 59,75</t>
+          <t>26,19; 62,89</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 21,62</t>
+          <t>-6,16; 21,28</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>72,96; 246,68</t>
+          <t>70,73; 109,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
